--- a/output/laminas_comunales/comunal_i_ingr_mean_a_2022_o_higgins.xlsx
+++ b/output/laminas_comunales/comunal_i_ingr_mean_a_2022_o_higgins.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -381,11 +381,6 @@
           <t>delta_pct</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>is_emph</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -396,9 +391,6 @@
       <c r="B2">
         <v>660681.5600000001</v>
       </c>
-      <c r="F2" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -409,9 +401,6 @@
       <c r="B3">
         <v>418011.53</v>
       </c>
-      <c r="F3" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -422,9 +411,6 @@
       <c r="B4">
         <v>378798.09</v>
       </c>
-      <c r="F4" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -435,9 +421,6 @@
       <c r="B5">
         <v>360435.72</v>
       </c>
-      <c r="F5" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -448,9 +431,6 @@
       <c r="B6">
         <v>345481.12</v>
       </c>
-      <c r="F6" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -461,9 +441,6 @@
       <c r="B7">
         <v>338389.34</v>
       </c>
-      <c r="F7" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -474,9 +451,6 @@
       <c r="B8">
         <v>337523.59</v>
       </c>
-      <c r="F8" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -487,9 +461,6 @@
       <c r="B9">
         <v>335281.41</v>
       </c>
-      <c r="F9" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -500,9 +471,6 @@
       <c r="B10">
         <v>308323.41</v>
       </c>
-      <c r="F10" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -513,9 +481,6 @@
       <c r="B11">
         <v>307132.94</v>
       </c>
-      <c r="F11" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -526,9 +491,6 @@
       <c r="B12">
         <v>295064.78</v>
       </c>
-      <c r="F12" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -539,9 +501,6 @@
       <c r="B13">
         <v>294327.22</v>
       </c>
-      <c r="F13" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -552,9 +511,6 @@
       <c r="B14">
         <v>283801.44</v>
       </c>
-      <c r="F14" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -565,9 +521,6 @@
       <c r="B15">
         <v>283513.53</v>
       </c>
-      <c r="F15" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -578,9 +531,6 @@
       <c r="B16">
         <v>282026.78</v>
       </c>
-      <c r="F16" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -591,9 +541,6 @@
       <c r="B17">
         <v>267550.44</v>
       </c>
-      <c r="F17" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -604,9 +551,6 @@
       <c r="B18">
         <v>267268.34</v>
       </c>
-      <c r="F18" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -617,9 +561,6 @@
       <c r="B19">
         <v>262971.69</v>
       </c>
-      <c r="F19" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -630,9 +571,6 @@
       <c r="B20">
         <v>260694</v>
       </c>
-      <c r="F20" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -643,9 +581,6 @@
       <c r="B21">
         <v>256763.7</v>
       </c>
-      <c r="F21" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -656,9 +591,6 @@
       <c r="B22">
         <v>250311.83</v>
       </c>
-      <c r="F22" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -669,9 +601,6 @@
       <c r="B23">
         <v>249196.61</v>
       </c>
-      <c r="F23" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -682,9 +611,6 @@
       <c r="B24">
         <v>249039.61</v>
       </c>
-      <c r="F24" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -695,9 +621,6 @@
       <c r="B25">
         <v>245511.33</v>
       </c>
-      <c r="F25" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -708,9 +631,6 @@
       <c r="B26">
         <v>244478.78</v>
       </c>
-      <c r="F26" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -721,9 +641,6 @@
       <c r="B27">
         <v>239836.97</v>
       </c>
-      <c r="F27" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -734,9 +651,6 @@
       <c r="B28">
         <v>228184.95</v>
       </c>
-      <c r="F28" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -747,9 +661,6 @@
       <c r="B29">
         <v>225821.28</v>
       </c>
-      <c r="F29" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -760,9 +671,6 @@
       <c r="B30">
         <v>215326.52</v>
       </c>
-      <c r="F30" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -773,9 +681,6 @@
       <c r="B31">
         <v>210052.19</v>
       </c>
-      <c r="F31" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -786,9 +691,6 @@
       <c r="B32">
         <v>206763.19</v>
       </c>
-      <c r="F32" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -799,9 +701,6 @@
       <c r="B33">
         <v>197771.22</v>
       </c>
-      <c r="F33" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -811,9 +710,6 @@
       </c>
       <c r="B34">
         <v>151215.36</v>
-      </c>
-      <c r="F34" t="b">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/laminas_comunales/comunal_i_ingr_mean_a_2022_o_higgins.xlsx
+++ b/output/laminas_comunales/comunal_i_ingr_mean_a_2022_o_higgins.xlsx
@@ -391,6 +391,15 @@
       <c r="B2">
         <v>660681.5600000001</v>
       </c>
+      <c r="C2">
+        <v>589428.6899999999</v>
+      </c>
+      <c r="D2">
+        <v>71252.87000000011</v>
+      </c>
+      <c r="E2">
+        <v>12.08846315234504</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -401,6 +410,15 @@
       <c r="B3">
         <v>418011.53</v>
       </c>
+      <c r="C3">
+        <v>361305.19</v>
+      </c>
+      <c r="D3">
+        <v>56706.34000000003</v>
+      </c>
+      <c r="E3">
+        <v>15.69485896396894</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -411,6 +429,15 @@
       <c r="B4">
         <v>378798.09</v>
       </c>
+      <c r="C4">
+        <v>310836.09</v>
+      </c>
+      <c r="D4">
+        <v>67962</v>
+      </c>
+      <c r="E4">
+        <v>21.86425649608448</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -421,6 +448,15 @@
       <c r="B5">
         <v>360435.72</v>
       </c>
+      <c r="C5">
+        <v>305404.97</v>
+      </c>
+      <c r="D5">
+        <v>55030.75</v>
+      </c>
+      <c r="E5">
+        <v>18.01894383054736</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -431,115 +467,223 @@
       <c r="B6">
         <v>345481.12</v>
       </c>
+      <c r="C6">
+        <v>298904.28</v>
+      </c>
+      <c r="D6">
+        <v>46576.83999999997</v>
+      </c>
+      <c r="E6">
+        <v>15.58252695478297</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Codegua</t>
+          <t>Promedio Regional</t>
         </is>
       </c>
       <c r="B7">
-        <v>338389.34</v>
+        <v>342759.81</v>
+      </c>
+      <c r="C7">
+        <v>294542.59</v>
+      </c>
+      <c r="D7">
+        <v>48217.21999999997</v>
+      </c>
+      <c r="E7">
+        <v>16.3702030324375</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>San Fernando</t>
+          <t>Codegua</t>
         </is>
       </c>
       <c r="B8">
-        <v>337523.59</v>
+        <v>338389.34</v>
+      </c>
+      <c r="C8">
+        <v>276345.25</v>
+      </c>
+      <c r="D8">
+        <v>62044.09000000003</v>
+      </c>
+      <c r="E8">
+        <v>22.45165784467076</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Doñihue</t>
+          <t>San Fernando</t>
         </is>
       </c>
       <c r="B9">
-        <v>335281.41</v>
+        <v>337523.59</v>
+      </c>
+      <c r="C9">
+        <v>293747.59</v>
+      </c>
+      <c r="D9">
+        <v>43776</v>
+      </c>
+      <c r="E9">
+        <v>14.90259034976253</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Mostazal</t>
+          <t>Doñihue</t>
         </is>
       </c>
       <c r="B10">
-        <v>308323.41</v>
+        <v>335281.41</v>
+      </c>
+      <c r="C10">
+        <v>293815.19</v>
+      </c>
+      <c r="D10">
+        <v>41466.21999999997</v>
+      </c>
+      <c r="E10">
+        <v>14.11302798878438</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Rengo</t>
+          <t>Mostazal</t>
         </is>
       </c>
       <c r="B11">
-        <v>307132.94</v>
+        <v>308323.41</v>
+      </c>
+      <c r="C11">
+        <v>256839.19</v>
+      </c>
+      <c r="D11">
+        <v>51484.21999999997</v>
+      </c>
+      <c r="E11">
+        <v>20.04531317825755</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Coltauco</t>
+          <t>Rengo</t>
         </is>
       </c>
       <c r="B12">
-        <v>295064.78</v>
+        <v>307132.94</v>
+      </c>
+      <c r="C12">
+        <v>260128.05</v>
+      </c>
+      <c r="D12">
+        <v>47004.89000000001</v>
+      </c>
+      <c r="E12">
+        <v>18.06990441822787</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Peumo</t>
+          <t>Coltauco</t>
         </is>
       </c>
       <c r="B13">
-        <v>294327.22</v>
+        <v>295064.78</v>
+      </c>
+      <c r="C13">
+        <v>239836.22</v>
+      </c>
+      <c r="D13">
+        <v>55228.56000000003</v>
+      </c>
+      <c r="E13">
+        <v>23.02761442787917</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Peumo</t>
         </is>
       </c>
       <c r="B14">
-        <v>283801.44</v>
+        <v>294327.22</v>
+      </c>
+      <c r="C14">
+        <v>256588.7</v>
+      </c>
+      <c r="D14">
+        <v>37738.51999999996</v>
+      </c>
+      <c r="E14">
+        <v>14.70778720964718</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Coinco</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="B15">
-        <v>283513.53</v>
+        <v>283801.44</v>
+      </c>
+      <c r="C15">
+        <v>242736.69</v>
+      </c>
+      <c r="D15">
+        <v>41064.75</v>
+      </c>
+      <c r="E15">
+        <v>16.91740544043836</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>San Vicente</t>
+          <t>Coinco</t>
         </is>
       </c>
       <c r="B16">
-        <v>282026.78</v>
+        <v>283513.53</v>
+      </c>
+      <c r="C16">
+        <v>241165.38</v>
+      </c>
+      <c r="D16">
+        <v>42348.15000000002</v>
+      </c>
+      <c r="E16">
+        <v>17.55979651805746</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Marchihue</t>
+          <t>San Vicente</t>
         </is>
       </c>
       <c r="B17">
-        <v>267550.44</v>
+        <v>282026.78</v>
+      </c>
+      <c r="C17">
+        <v>241836.22</v>
+      </c>
+      <c r="D17">
+        <v>40190.56000000003</v>
+      </c>
+      <c r="E17">
+        <v>16.61891671975357</v>
       </c>
     </row>
     <row r="18">
@@ -551,6 +695,15 @@
       <c r="B18">
         <v>267268.34</v>
       </c>
+      <c r="C18">
+        <v>221196.34</v>
+      </c>
+      <c r="D18">
+        <v>46072.00000000003</v>
+      </c>
+      <c r="E18">
+        <v>20.8285543965149</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -561,6 +714,15 @@
       <c r="B19">
         <v>262971.69</v>
       </c>
+      <c r="C19">
+        <v>220061.69</v>
+      </c>
+      <c r="D19">
+        <v>42910</v>
+      </c>
+      <c r="E19">
+        <v>19.49907773588397</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -571,6 +733,15 @@
       <c r="B20">
         <v>260694</v>
       </c>
+      <c r="C20">
+        <v>219203.42</v>
+      </c>
+      <c r="D20">
+        <v>41490.57999999999</v>
+      </c>
+      <c r="E20">
+        <v>18.92788899005316</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -581,6 +752,15 @@
       <c r="B21">
         <v>256763.7</v>
       </c>
+      <c r="C21">
+        <v>210347.52</v>
+      </c>
+      <c r="D21">
+        <v>46416.18000000002</v>
+      </c>
+      <c r="E21">
+        <v>22.06642607433642</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -591,6 +771,15 @@
       <c r="B22">
         <v>250311.83</v>
       </c>
+      <c r="C22">
+        <v>212444.98</v>
+      </c>
+      <c r="D22">
+        <v>37866.84999999998</v>
+      </c>
+      <c r="E22">
+        <v>17.82430914583153</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -601,6 +790,15 @@
       <c r="B23">
         <v>249196.61</v>
       </c>
+      <c r="C23">
+        <v>212108.17</v>
+      </c>
+      <c r="D23">
+        <v>37088.43999999997</v>
+      </c>
+      <c r="E23">
+        <v>17.48562537690084</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -611,6 +809,15 @@
       <c r="B24">
         <v>249039.61</v>
       </c>
+      <c r="C24">
+        <v>216252.31</v>
+      </c>
+      <c r="D24">
+        <v>32787.29999999999</v>
+      </c>
+      <c r="E24">
+        <v>15.16159526804593</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -621,6 +828,15 @@
       <c r="B25">
         <v>245511.33</v>
       </c>
+      <c r="C25">
+        <v>193565.09</v>
+      </c>
+      <c r="D25">
+        <v>51946.23999999999</v>
+      </c>
+      <c r="E25">
+        <v>26.83657471499639</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -631,6 +847,15 @@
       <c r="B26">
         <v>244478.78</v>
       </c>
+      <c r="C26">
+        <v>200711.84</v>
+      </c>
+      <c r="D26">
+        <v>43766.94</v>
+      </c>
+      <c r="E26">
+        <v>21.80585858811319</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -641,6 +866,15 @@
       <c r="B27">
         <v>239836.97</v>
       </c>
+      <c r="C27">
+        <v>202594.69</v>
+      </c>
+      <c r="D27">
+        <v>37242.28</v>
+      </c>
+      <c r="E27">
+        <v>18.3826535631314</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -651,6 +885,15 @@
       <c r="B28">
         <v>228184.95</v>
       </c>
+      <c r="C28">
+        <v>192007.03</v>
+      </c>
+      <c r="D28">
+        <v>36177.92000000001</v>
+      </c>
+      <c r="E28">
+        <v>18.84197677553785</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -661,6 +904,15 @@
       <c r="B29">
         <v>225821.28</v>
       </c>
+      <c r="C29">
+        <v>181864.47</v>
+      </c>
+      <c r="D29">
+        <v>43956.81</v>
+      </c>
+      <c r="E29">
+        <v>24.17009215708818</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -671,6 +923,15 @@
       <c r="B30">
         <v>215326.52</v>
       </c>
+      <c r="C30">
+        <v>184974.33</v>
+      </c>
+      <c r="D30">
+        <v>30352.19</v>
+      </c>
+      <c r="E30">
+        <v>16.4088660302216</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -681,6 +942,15 @@
       <c r="B31">
         <v>210052.19</v>
       </c>
+      <c r="C31">
+        <v>170319.27</v>
+      </c>
+      <c r="D31">
+        <v>39732.92000000001</v>
+      </c>
+      <c r="E31">
+        <v>23.32849359910949</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -691,6 +961,15 @@
       <c r="B32">
         <v>206763.19</v>
       </c>
+      <c r="C32">
+        <v>174272.94</v>
+      </c>
+      <c r="D32">
+        <v>32490.25</v>
+      </c>
+      <c r="E32">
+        <v>18.64331318447947</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -701,6 +980,15 @@
       <c r="B33">
         <v>197771.22</v>
       </c>
+      <c r="C33">
+        <v>174781.55</v>
+      </c>
+      <c r="D33">
+        <v>22989.67000000001</v>
+      </c>
+      <c r="E33">
+        <v>13.15337345389145</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -710,6 +998,15 @@
       </c>
       <c r="B34">
         <v>151215.36</v>
+      </c>
+      <c r="C34">
+        <v>133262.55</v>
+      </c>
+      <c r="D34">
+        <v>17952.81</v>
+      </c>
+      <c r="E34">
+        <v>13.47175932022913</v>
       </c>
     </row>
   </sheetData>
@@ -719,7 +1016,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B34"/>
+  <dimension ref="A1:B33"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -867,200 +1164,190 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Marchihue</t>
+          <t>Mostazal</t>
         </is>
       </c>
       <c r="B15">
-        <v>267550.44</v>
+        <v>308323.41</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Mostazal</t>
+          <t>Nancagua</t>
         </is>
       </c>
       <c r="B16">
-        <v>308323.41</v>
+        <v>250311.83</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Nancagua</t>
+          <t>Navidad</t>
         </is>
       </c>
       <c r="B17">
-        <v>250311.83</v>
+        <v>225821.28</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Navidad</t>
+          <t>Olivar</t>
         </is>
       </c>
       <c r="B18">
-        <v>225821.28</v>
+        <v>360435.72</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Olivar</t>
+          <t>Palmilla</t>
         </is>
       </c>
       <c r="B19">
-        <v>360435.72</v>
+        <v>249196.61</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Palmilla</t>
+          <t>Paredones</t>
         </is>
       </c>
       <c r="B20">
-        <v>249196.61</v>
+        <v>151215.36</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Paredones</t>
+          <t>Peralillo</t>
         </is>
       </c>
       <c r="B21">
-        <v>151215.36</v>
+        <v>262971.69</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Peralillo</t>
+          <t>Peumo</t>
         </is>
       </c>
       <c r="B22">
-        <v>262971.69</v>
+        <v>294327.22</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Peumo</t>
+          <t>Pichidegua</t>
         </is>
       </c>
       <c r="B23">
-        <v>294327.22</v>
+        <v>249039.61</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Pichidegua</t>
+          <t>Pichilemu</t>
         </is>
       </c>
       <c r="B24">
-        <v>249039.61</v>
+        <v>245511.33</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Pichilemu</t>
+          <t>Placilla</t>
         </is>
       </c>
       <c r="B25">
-        <v>245511.33</v>
+        <v>256763.7</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Placilla</t>
+          <t>Pumanque</t>
         </is>
       </c>
       <c r="B26">
-        <v>256763.7</v>
+        <v>210052.19</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Pumanque</t>
+          <t>Quinta de Tilcoco</t>
         </is>
       </c>
       <c r="B27">
-        <v>210052.19</v>
+        <v>244478.78</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Quinta de Tilcoco</t>
+          <t>Rancagua</t>
         </is>
       </c>
       <c r="B28">
-        <v>244478.78</v>
+        <v>418011.53</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Rancagua</t>
+          <t>Rengo</t>
         </is>
       </c>
       <c r="B29">
-        <v>418011.53</v>
+        <v>307132.94</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Rengo</t>
+          <t>Requínoa</t>
         </is>
       </c>
       <c r="B30">
-        <v>307132.94</v>
+        <v>378798.09</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Requínoa</t>
+          <t>San Fernando</t>
         </is>
       </c>
       <c r="B31">
-        <v>378798.09</v>
+        <v>337523.59</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>San Fernando</t>
+          <t>San Vicente</t>
         </is>
       </c>
       <c r="B32">
-        <v>337523.59</v>
+        <v>282026.78</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>San Vicente</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="B33">
-        <v>282026.78</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Santa Cruz</t>
-        </is>
-      </c>
-      <c r="B34">
         <v>283801.44</v>
       </c>
     </row>

--- a/output/laminas_comunales/comunal_i_ingr_mean_a_2022_o_higgins.xlsx
+++ b/output/laminas_comunales/comunal_i_ingr_mean_a_2022_o_higgins.xlsx
@@ -1016,7 +1016,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B33"/>
+  <dimension ref="A1:A34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1025,330 +1025,236 @@
           <t>Comuna</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Chépica</t>
-        </is>
-      </c>
-      <c r="B2">
-        <v>206763.19</v>
+          <t>Marchigüe</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Chimbarongo</t>
-        </is>
-      </c>
-      <c r="B3">
-        <v>260694</v>
+          <t>Codegua</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Codegua</t>
-        </is>
-      </c>
-      <c r="B4">
-        <v>338389.34</v>
+          <t>Coinco</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Coinco</t>
-        </is>
-      </c>
-      <c r="B5">
-        <v>283513.53</v>
+          <t>Coltauco</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Coltauco</t>
-        </is>
-      </c>
-      <c r="B6">
-        <v>295064.78</v>
+          <t>Graneros</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Doñihue</t>
-        </is>
-      </c>
-      <c r="B7">
-        <v>335281.41</v>
+          <t>Malloa</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Graneros</t>
-        </is>
-      </c>
-      <c r="B8">
-        <v>345481.12</v>
+          <t>Peumo</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>La Estrella</t>
-        </is>
-      </c>
-      <c r="B9">
-        <v>215326.52</v>
+          <t>Pichidegua</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Las Cabras</t>
-        </is>
-      </c>
-      <c r="B10">
-        <v>267268.34</v>
+          <t>Rancagua</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Litueche</t>
-        </is>
-      </c>
-      <c r="B11">
-        <v>228184.95</v>
+          <t>Requínoa</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Lolol</t>
-        </is>
-      </c>
-      <c r="B12">
-        <v>197771.22</v>
+          <t>Mostazal</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Machalí</t>
-        </is>
-      </c>
-      <c r="B13">
-        <v>660681.5600000001</v>
+          <t>San Vicente</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Malloa</t>
-        </is>
-      </c>
-      <c r="B14">
-        <v>239836.97</v>
+          <t>Nancagua</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Mostazal</t>
-        </is>
-      </c>
-      <c r="B15">
-        <v>308323.41</v>
+          <t>Peralillo</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Nancagua</t>
-        </is>
-      </c>
-      <c r="B16">
-        <v>250311.83</v>
+          <t>Placilla</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Navidad</t>
-        </is>
-      </c>
-      <c r="B17">
-        <v>225821.28</v>
+          <t>Pumanque</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Olivar</t>
-        </is>
-      </c>
-      <c r="B18">
-        <v>360435.72</v>
+          <t>Paredones</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Palmilla</t>
-        </is>
-      </c>
-      <c r="B19">
-        <v>249196.61</v>
+          <t>Pichilemu</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Paredones</t>
-        </is>
-      </c>
-      <c r="B20">
-        <v>151215.36</v>
+          <t>Litueche</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Peralillo</t>
-        </is>
-      </c>
-      <c r="B21">
-        <v>262971.69</v>
+          <t>Navidad</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Peumo</t>
-        </is>
-      </c>
-      <c r="B22">
-        <v>294327.22</v>
+          <t>La Estrella</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Pichidegua</t>
-        </is>
-      </c>
-      <c r="B23">
-        <v>249039.61</v>
+          <t>Doñihue</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Pichilemu</t>
-        </is>
-      </c>
-      <c r="B24">
-        <v>245511.33</v>
+          <t>Olivar</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Placilla</t>
-        </is>
-      </c>
-      <c r="B25">
-        <v>256763.7</v>
+          <t>Rengo</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Pumanque</t>
-        </is>
-      </c>
-      <c r="B26">
-        <v>210052.19</v>
+          <t>Santa Cruz</t>
+        </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Quinta de Tilcoco</t>
-        </is>
-      </c>
-      <c r="B27">
-        <v>244478.78</v>
+          <t>Palmilla</t>
+        </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rancagua</t>
-        </is>
-      </c>
-      <c r="B28">
-        <v>418011.53</v>
+          <t>Quinta de Tilcoco</t>
+        </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Rengo</t>
-        </is>
-      </c>
-      <c r="B29">
-        <v>307132.94</v>
+          <t>Machalí</t>
+        </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Requínoa</t>
-        </is>
-      </c>
-      <c r="B30">
-        <v>378798.09</v>
+          <t>Las Cabras</t>
+        </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>San Fernando</t>
-        </is>
-      </c>
-      <c r="B31">
-        <v>337523.59</v>
+          <t>Chimbarongo</t>
+        </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>San Vicente</t>
-        </is>
-      </c>
-      <c r="B32">
-        <v>282026.78</v>
+          <t>Lolol</t>
+        </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
-        </is>
-      </c>
-      <c r="B33">
-        <v>283801.44</v>
+          <t>Chépica</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>San Fernando</t>
+        </is>
       </c>
     </row>
   </sheetData>
